--- a/server/data/xlsx/CharacterClassData.xlsx
+++ b/server/data/xlsx/CharacterClassData.xlsx
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
         <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -679,25 +679,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
